--- a/vectorCards.xlsx
+++ b/vectorCards.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,10 @@
       <b val="1"/>
       <color rgb="00FFAA00"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -127,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +174,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2329,6 +2336,60 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>WormHole</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Felaket</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>5s: Opens a wormhole in front of Vector. Approaching enemies are teleported (Boss immune). Score x0.5.</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>5s: Vector onunde solucan deligi acar. Yaklasan dusmanlar isinlanir (Boss hariç). Skor x0.5.</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Efsanevi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Siege Rain</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Felaket</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>7s: Every 0.5s a Siege Core falls on the target area dealing AoE damage. Screen shake + ground crack VFX.</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>7s: Her 0.5s hedef alana Siege Core duser, alan hasari uygular. Ekran sarsintisi + zemin catlagi.</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Efsanevi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>

--- a/vectorCards.xlsx
+++ b/vectorCards.xlsx
@@ -924,12 +924,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Armor %75+ doluyken: | 90px düşmanlar %25 yavaşlar</t>
+          <t>Armor %75+ doluyken: 90px icindeki tum dusmanlara surekli %25 yavaslatma uygular</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Zırh %75+: 90px yavaşlatma %25 (1s)</t>
+          <t>Armor %75+: 90px'e surekli %25 yavaslatma</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
